--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-26T08:27:54+00:00</t>
+    <t>2023-04-26T14:43:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-26T14:43:04+00:00</t>
+    <t>2023-04-27T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-27T16:49:23+00:00</t>
+    <t>2023-05-02T12:59:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T12:59:07+00:00</t>
+    <t>2023-05-02T13:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T13:06:55+00:00</t>
+    <t>2023-05-02T14:05:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:33:57+00:00</t>
+    <t>2023-07-18T09:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:34:12+00:00</t>
+    <t>2023-07-18T09:34:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:34:49+00:00</t>
+    <t>2023-07-18T09:37:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-19T16:09:26+00:00</t>
+    <t>2023-09-19T16:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-19T16:18:04+00:00</t>
+    <t>2023-09-20T15:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T15:08:45+00:00</t>
+    <t>2023-09-27T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:45:14+00:00</t>
+    <t>2023-11-23T10:14:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:44:29+00:00</t>
+    <t>2023-11-28T13:07:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:18:47+00:00</t>
+    <t>2023-11-28T13:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7234" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7234" uniqueCount="786">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:27:45+00:00</t>
+    <t>2023-11-28T13:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1020,9 +1020,6 @@
   </si>
   <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Signes vitaux</t>
   </si>
   <si>
     <t>Coding.display</t>
@@ -7083,46 +7080,46 @@
         <v>81</v>
       </c>
       <c r="S36" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="T36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -7143,10 +7140,10 @@
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -7157,10 +7154,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7183,19 +7180,19 @@
         <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -7244,7 +7241,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -7265,10 +7262,10 @@
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
@@ -7279,10 +7276,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7308,16 +7305,16 @@
         <v>108</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -7366,7 +7363,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -7387,10 +7384,10 @@
         <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
@@ -7401,14 +7398,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7430,16 +7427,16 @@
         <v>260</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M39" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -7467,11 +7464,11 @@
         <v>152</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>352</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
       </c>
@@ -7488,7 +7485,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>92</v>
@@ -7503,30 +7500,30 @@
         <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AO39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>358</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7641,10 +7638,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7761,10 +7758,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7836,7 +7833,7 @@
         <v>81</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
@@ -7881,13 +7878,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="C43" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>81</v>
@@ -8005,10 +8002,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8123,10 +8120,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8243,10 +8240,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8288,7 +8285,7 @@
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>81</v>
@@ -8365,10 +8362,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8485,10 +8482,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8530,7 +8527,7 @@
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>81</v>
@@ -8607,10 +8604,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8694,7 +8691,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8715,10 +8712,10 @@
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>81</v>
@@ -8729,10 +8726,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8755,19 +8752,19 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -8816,7 +8813,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8837,10 +8834,10 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>81</v>
@@ -8851,10 +8848,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8880,16 +8877,16 @@
         <v>108</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8938,7 +8935,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8959,10 +8956,10 @@
         <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>81</v>
@@ -8973,10 +8970,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8999,19 +8996,19 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -9060,7 +9057,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -9075,19 +9072,19 @@
         <v>233</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>81</v>
@@ -9095,10 +9092,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9121,16 +9118,16 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9180,7 +9177,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -9201,13 +9198,13 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>81</v>
@@ -9215,14 +9212,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -9241,19 +9238,19 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -9302,7 +9299,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -9317,19 +9314,19 @@
         <v>233</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AL54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>81</v>
@@ -9337,14 +9334,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9363,19 +9360,19 @@
         <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -9424,7 +9421,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -9439,19 +9436,19 @@
         <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AL55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>81</v>
@@ -9459,10 +9456,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9488,13 +9485,13 @@
         <v>130</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9544,7 +9541,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -9565,13 +9562,13 @@
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>81</v>
@@ -9579,10 +9576,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9605,19 +9602,19 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>231</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -9666,7 +9663,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9681,19 +9678,19 @@
         <v>233</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>81</v>
@@ -9701,10 +9698,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9727,19 +9724,19 @@
         <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -9788,7 +9785,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9797,7 +9794,7 @@
         <v>92</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
@@ -9806,27 +9803,27 @@
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9852,16 +9849,16 @@
         <v>260</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
@@ -9889,37 +9886,37 @@
         <v>152</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="Z59" t="s" s="2">
+      <c r="AA59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI59" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
@@ -9934,7 +9931,7 @@
         <v>106</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -9945,14 +9942,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9974,16 +9971,16 @@
         <v>260</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -10012,7 +10009,7 @@
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -10030,7 +10027,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -10048,27 +10045,27 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>465</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10091,19 +10088,19 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -10152,7 +10149,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -10173,10 +10170,10 @@
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>81</v>
@@ -10187,10 +10184,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10216,13 +10213,13 @@
         <v>260</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10251,10 +10248,10 @@
         <v>251</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -10272,7 +10269,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -10290,27 +10287,27 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AN62" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>482</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10425,10 +10422,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10545,10 +10542,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10667,10 +10664,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10785,10 +10782,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10905,10 +10902,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11027,10 +11024,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11147,10 +11144,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11269,10 +11266,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11356,7 +11353,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -11377,10 +11374,10 @@
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>81</v>
@@ -11391,10 +11388,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11417,19 +11414,19 @@
         <v>93</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11478,7 +11475,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -11499,10 +11496,10 @@
         <v>81</v>
       </c>
       <c r="AM72" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>81</v>
@@ -11513,10 +11510,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11542,16 +11539,16 @@
         <v>108</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="N73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>81</v>
@@ -11600,7 +11597,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -11621,10 +11618,10 @@
         <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>81</v>
@@ -11635,10 +11632,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11664,16 +11661,16 @@
         <v>260</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11702,7 +11699,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>81</v>
@@ -11720,7 +11717,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11741,10 +11738,10 @@
         <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>81</v>
@@ -11755,10 +11752,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11781,16 +11778,16 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11840,7 +11837,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11858,27 +11855,27 @@
         <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AN75" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AN75" t="s" s="2">
+      <c r="AO75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP75" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>510</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11901,16 +11898,16 @@
         <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11960,7 +11957,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11978,27 +11975,27 @@
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="AM76" t="s" s="2">
+      <c r="AN76" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>519</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12021,19 +12018,19 @@
         <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12082,7 +12079,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -12094,19 +12091,19 @@
         <v>104</v>
       </c>
       <c r="AJ77" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AK77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM77" t="s" s="2">
+      <c r="AN77" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>81</v>
@@ -12117,10 +12114,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12235,10 +12232,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12355,14 +12352,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -12384,10 +12381,10 @@
         <v>115</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>118</v>
@@ -12442,7 +12439,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -12477,10 +12474,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12503,16 +12500,16 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12562,7 +12559,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -12571,22 +12568,22 @@
         <v>92</v>
       </c>
       <c r="AI81" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="AJ81" t="s" s="2">
+      <c r="AK81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM81" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="AK81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM81" t="s" s="2">
+      <c r="AN81" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>81</v>
@@ -12597,10 +12594,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12623,16 +12620,16 @@
         <v>81</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="M82" t="s" s="2">
-        <v>547</v>
-      </c>
       <c r="N82" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12682,7 +12679,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12691,22 +12688,22 @@
         <v>92</v>
       </c>
       <c r="AI82" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="AJ82" t="s" s="2">
+      <c r="AK82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM82" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="AK82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>543</v>
-      </c>
       <c r="AN82" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>81</v>
@@ -12717,10 +12714,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12746,16 +12743,16 @@
         <v>260</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -12783,11 +12780,11 @@
         <v>176</v>
       </c>
       <c r="Y83" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="Z83" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="Z83" t="s" s="2">
-        <v>555</v>
-      </c>
       <c r="AA83" t="s" s="2">
         <v>81</v>
       </c>
@@ -12804,7 +12801,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12822,13 +12819,13 @@
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AM83" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="AM83" t="s" s="2">
-        <v>557</v>
-      </c>
       <c r="AN83" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>81</v>
@@ -12839,10 +12836,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12868,16 +12865,16 @@
         <v>260</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -12905,10 +12902,10 @@
         <v>251</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>81</v>
@@ -12926,7 +12923,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12944,13 +12941,13 @@
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="AM84" t="s" s="2">
-        <v>557</v>
-      </c>
       <c r="AN84" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>81</v>
@@ -12961,10 +12958,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13079,10 +13076,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13199,10 +13196,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13321,10 +13318,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13439,10 +13436,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13559,10 +13556,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13681,10 +13678,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13801,10 +13798,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13923,10 +13920,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14010,7 +14007,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -14031,10 +14028,10 @@
         <v>81</v>
       </c>
       <c r="AM93" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>81</v>
@@ -14045,10 +14042,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14071,19 +14068,19 @@
         <v>93</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14132,7 +14129,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -14153,10 +14150,10 @@
         <v>81</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>81</v>
@@ -14167,10 +14164,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14196,16 +14193,16 @@
         <v>108</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="N95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14254,7 +14251,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -14275,10 +14272,10 @@
         <v>81</v>
       </c>
       <c r="AM95" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>81</v>
@@ -14289,10 +14286,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14315,19 +14312,19 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>81</v>
@@ -14376,7 +14373,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -14388,19 +14385,19 @@
         <v>104</v>
       </c>
       <c r="AJ96" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM96" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="AK96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM96" t="s" s="2">
+      <c r="AN96" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>81</v>
@@ -14411,10 +14408,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14440,10 +14437,10 @@
         <v>108</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>312</v>
@@ -14496,7 +14493,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -14517,10 +14514,10 @@
         <v>81</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>81</v>
@@ -14531,10 +14528,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14557,16 +14554,16 @@
         <v>93</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="M98" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14616,7 +14613,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -14637,10 +14634,10 @@
         <v>81</v>
       </c>
       <c r="AM98" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>81</v>
@@ -14651,10 +14648,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14677,16 +14674,16 @@
         <v>93</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14736,7 +14733,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14757,10 +14754,10 @@
         <v>81</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>81</v>
@@ -14771,10 +14768,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14782,7 +14779,7 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>80</v>
@@ -14797,19 +14794,19 @@
         <v>93</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>81</v>
@@ -14846,7 +14843,7 @@
         <v>81</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AC100" s="2"/>
       <c r="AD100" t="s" s="2">
@@ -14856,7 +14853,7 @@
         <v>121</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14877,10 +14874,10 @@
         <v>81</v>
       </c>
       <c r="AM100" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AN100" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>81</v>
@@ -14891,10 +14888,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15009,10 +15006,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15129,14 +15126,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -15158,10 +15155,10 @@
         <v>115</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="N103" t="s" s="2">
         <v>118</v>
@@ -15216,7 +15213,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -15251,10 +15248,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15280,16 +15277,16 @@
         <v>260</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="N104" t="s" s="2">
-        <v>616</v>
-      </c>
       <c r="O104" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>81</v>
@@ -15317,10 +15314,10 @@
         <v>162</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>81</v>
@@ -15338,7 +15335,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>92</v>
@@ -15356,16 +15353,16 @@
         <v>81</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AM104" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AN104" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AN104" t="s" s="2">
+      <c r="AO104" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15373,10 +15370,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15399,19 +15396,19 @@
         <v>93</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="M105" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>621</v>
-      </c>
       <c r="O105" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>81</v>
@@ -15460,7 +15457,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -15478,27 +15475,27 @@
         <v>81</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AM105" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AN105" t="s" s="2">
+      <c r="AO105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP105" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP105" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15524,16 +15521,16 @@
         <v>260</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="N106" t="s" s="2">
-        <v>626</v>
-      </c>
       <c r="O106" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>81</v>
@@ -15561,37 +15558,37 @@
         <v>152</v>
       </c>
       <c r="Y106" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="Z106" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="Z106" t="s" s="2">
+      <c r="AA106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI106" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>105</v>
@@ -15606,7 +15603,7 @@
         <v>106</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>81</v>
@@ -15617,14 +15614,14 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -15646,16 +15643,16 @@
         <v>260</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>81</v>
@@ -15683,10 +15680,10 @@
         <v>152</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>81</v>
@@ -15704,7 +15701,7 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -15722,27 +15719,27 @@
         <v>81</v>
       </c>
       <c r="AL107" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AM107" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AM107" t="s" s="2">
+      <c r="AN107" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AN107" t="s" s="2">
+      <c r="AO107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP107" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>465</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15768,16 +15765,16 @@
         <v>82</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="M108" t="s" s="2">
-        <v>631</v>
-      </c>
       <c r="N108" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O108" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>81</v>
@@ -15826,7 +15823,7 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -15847,10 +15844,10 @@
         <v>81</v>
       </c>
       <c r="AM108" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>81</v>
@@ -15861,13 +15858,13 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C109" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="C109" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>81</v>
@@ -15889,19 +15886,19 @@
         <v>93</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="N109" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="O109" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>81</v>
@@ -15950,7 +15947,7 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15971,10 +15968,10 @@
         <v>81</v>
       </c>
       <c r="AM109" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AN109" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>81</v>
@@ -15985,10 +15982,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16103,10 +16100,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16223,14 +16220,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -16252,10 +16249,10 @@
         <v>115</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>118</v>
@@ -16310,7 +16307,7 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -16345,10 +16342,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16374,16 +16371,16 @@
         <v>260</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="N113" t="s" s="2">
-        <v>616</v>
-      </c>
       <c r="O113" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>81</v>
@@ -16411,10 +16408,10 @@
         <v>162</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>81</v>
@@ -16432,7 +16429,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>92</v>
@@ -16450,16 +16447,16 @@
         <v>81</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AM113" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AN113" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AN113" t="s" s="2">
+      <c r="AO113" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AO113" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>81</v>
@@ -16467,10 +16464,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B114" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16585,10 +16582,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="B115" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16705,10 +16702,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="B116" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16734,10 +16731,10 @@
         <v>148</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>281</v>
@@ -16780,7 +16777,7 @@
         <v>81</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AC116" s="2"/>
       <c r="AD116" t="s" s="2">
@@ -16825,13 +16822,13 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="C117" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>81</v>
@@ -16949,10 +16946,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="B118" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17067,10 +17064,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="B119" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17187,10 +17184,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B120" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17232,7 +17229,7 @@
       </c>
       <c r="Q120" s="2"/>
       <c r="R120" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="S120" t="s" s="2">
         <v>81</v>
@@ -17309,10 +17306,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="B121" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17429,10 +17426,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="B122" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17474,7 +17471,7 @@
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>81</v>
@@ -17551,10 +17548,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="B123" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17638,7 +17635,7 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -17659,10 +17656,10 @@
         <v>81</v>
       </c>
       <c r="AM123" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AN123" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>81</v>
@@ -17673,10 +17670,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="B124" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>662</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17699,19 +17696,19 @@
         <v>93</v>
       </c>
       <c r="K124" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L124" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L124" t="s" s="2">
+      <c r="M124" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="N124" t="s" s="2">
+      <c r="O124" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>81</v>
@@ -17760,7 +17757,7 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17781,10 +17778,10 @@
         <v>81</v>
       </c>
       <c r="AM124" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AN124" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>81</v>
@@ -17795,10 +17792,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="B125" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17824,16 +17821,16 @@
         <v>108</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="N125" t="s" s="2">
+      <c r="O125" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>81</v>
@@ -17882,7 +17879,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17903,10 +17900,10 @@
         <v>81</v>
       </c>
       <c r="AM125" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AN125" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>81</v>
@@ -17917,10 +17914,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17943,19 +17940,19 @@
         <v>93</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>81</v>
@@ -17983,11 +17980,11 @@
         <v>251</v>
       </c>
       <c r="Y126" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="Z126" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="Z126" t="s" s="2">
-        <v>668</v>
-      </c>
       <c r="AA126" t="s" s="2">
         <v>81</v>
       </c>
@@ -18004,7 +18001,7 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -18022,30 +18019,30 @@
         <v>81</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AM126" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AN126" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AN126" t="s" s="2">
+      <c r="AO126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP126" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP126" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="C127" t="s" s="2">
         <v>669</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="C127" t="s" s="2">
-        <v>670</v>
       </c>
       <c r="D127" t="s" s="2">
         <v>81</v>
@@ -18067,19 +18064,19 @@
         <v>93</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N127" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="M127" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>621</v>
-      </c>
       <c r="O127" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>81</v>
@@ -18128,7 +18125,7 @@
         <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -18146,27 +18143,27 @@
         <v>81</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AM127" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AN127" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AN127" t="s" s="2">
+      <c r="AO127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP127" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AO127" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP127" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="B128" t="s" s="2">
         <v>672</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>673</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18281,10 +18278,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="B129" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>675</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18401,10 +18398,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="B130" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18427,19 +18424,19 @@
         <v>93</v>
       </c>
       <c r="K130" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="L130" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="L130" t="s" s="2">
+      <c r="M130" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="M130" t="s" s="2">
+      <c r="N130" t="s" s="2">
         <v>680</v>
       </c>
-      <c r="N130" t="s" s="2">
+      <c r="O130" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>81</v>
@@ -18488,7 +18485,7 @@
         <v>81</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -18509,10 +18506,10 @@
         <v>81</v>
       </c>
       <c r="AM130" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="AN130" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="AN130" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>81</v>
@@ -18523,10 +18520,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="B131" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18552,22 +18549,22 @@
         <v>172</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>689</v>
       </c>
       <c r="N131" t="s" s="2">
         <v>312</v>
       </c>
       <c r="O131" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="P131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q131" t="s" s="2">
         <v>690</v>
-      </c>
-      <c r="P131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q131" t="s" s="2">
-        <v>691</v>
       </c>
       <c r="R131" t="s" s="2">
         <v>81</v>
@@ -18591,28 +18588,28 @@
         <v>251</v>
       </c>
       <c r="Y131" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="Z131" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="Z131" t="s" s="2">
+      <c r="AA131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF131" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -18633,10 +18630,10 @@
         <v>81</v>
       </c>
       <c r="AM131" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AN131" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>696</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>81</v>
@@ -18647,10 +18644,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="B132" t="s" s="2">
         <v>697</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>698</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18676,65 +18673,65 @@
         <v>108</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>700</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>312</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF132" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="S132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18755,10 +18752,10 @@
         <v>81</v>
       </c>
       <c r="AM132" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="AN132" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>81</v>
@@ -18769,10 +18766,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="B133" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18798,74 +18795,74 @@
         <v>136</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>708</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>709</v>
       </c>
-      <c r="N133" t="s" s="2">
+      <c r="O133" t="s" s="2">
         <v>710</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>711</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q133" s="2"/>
       <c r="R133" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF133" t="s" s="2">
         <v>712</v>
       </c>
-      <c r="S133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF133" t="s" s="2">
+      <c r="AG133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI133" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>105</v>
@@ -18877,10 +18874,10 @@
         <v>81</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>81</v>
@@ -18891,10 +18888,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="B134" t="s" s="2">
         <v>716</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18920,23 +18917,23 @@
         <v>172</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>718</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>719</v>
       </c>
-      <c r="N134" t="s" s="2">
+      <c r="O134" t="s" s="2">
         <v>720</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>721</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q134" s="2"/>
       <c r="R134" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="S134" t="s" s="2">
         <v>81</v>
@@ -18978,7 +18975,7 @@
         <v>81</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18999,10 +18996,10 @@
         <v>81</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>81</v>
@@ -19013,10 +19010,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19042,16 +19039,16 @@
         <v>260</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="N135" t="s" s="2">
-        <v>626</v>
-      </c>
       <c r="O135" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>81</v>
@@ -19079,37 +19076,37 @@
         <v>152</v>
       </c>
       <c r="Y135" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="Z135" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="Z135" t="s" s="2">
+      <c r="AA135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI135" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="AG135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH135" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI135" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AJ135" t="s" s="2">
         <v>105</v>
@@ -19124,7 +19121,7 @@
         <v>106</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>81</v>
@@ -19135,14 +19132,14 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
@@ -19164,16 +19161,16 @@
         <v>260</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="N136" t="s" s="2">
+      <c r="O136" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>81</v>
@@ -19201,10 +19198,10 @@
         <v>152</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>81</v>
@@ -19222,7 +19219,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -19240,27 +19237,27 @@
         <v>81</v>
       </c>
       <c r="AL136" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AM136" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AM136" t="s" s="2">
+      <c r="AN136" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AN136" t="s" s="2">
+      <c r="AO136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP136" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AO136" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP136" t="s" s="2">
-        <v>465</v>
       </c>
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19286,16 +19283,16 @@
         <v>82</v>
       </c>
       <c r="L137" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M137" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="M137" t="s" s="2">
-        <v>631</v>
-      </c>
       <c r="N137" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O137" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>81</v>
@@ -19344,7 +19341,7 @@
         <v>81</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -19365,10 +19362,10 @@
         <v>81</v>
       </c>
       <c r="AM137" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AN137" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AN137" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>81</v>
@@ -19379,13 +19376,13 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C138" t="s" s="2">
         <v>728</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="C138" t="s" s="2">
-        <v>729</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>81</v>
@@ -19407,19 +19404,19 @@
         <v>93</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="N138" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="O138" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>81</v>
@@ -19468,7 +19465,7 @@
         <v>81</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -19489,10 +19486,10 @@
         <v>81</v>
       </c>
       <c r="AM138" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AN138" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="AN138" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>81</v>
@@ -19503,10 +19500,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19621,10 +19618,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19741,14 +19738,14 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -19770,10 +19767,10 @@
         <v>115</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="N141" t="s" s="2">
         <v>118</v>
@@ -19828,7 +19825,7 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19863,10 +19860,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19892,16 +19889,16 @@
         <v>260</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="M142" t="s" s="2">
+      <c r="N142" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="N142" t="s" s="2">
-        <v>616</v>
-      </c>
       <c r="O142" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>81</v>
@@ -19929,10 +19926,10 @@
         <v>162</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>81</v>
@@ -19950,7 +19947,7 @@
         <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>92</v>
@@ -19968,16 +19965,16 @@
         <v>81</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AM142" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AN142" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AN142" t="s" s="2">
+      <c r="AO142" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AO142" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AP142" t="s" s="2">
         <v>81</v>
@@ -19985,10 +19982,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20103,10 +20100,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20223,10 +20220,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20298,7 +20295,7 @@
         <v>81</v>
       </c>
       <c r="AB145" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AC145" s="2"/>
       <c r="AD145" t="s" s="2">
@@ -20343,13 +20340,13 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="C146" t="s" s="2">
         <v>738</v>
-      </c>
-      <c r="B146" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="C146" t="s" s="2">
-        <v>739</v>
       </c>
       <c r="D146" t="s" s="2">
         <v>81</v>
@@ -20467,10 +20464,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20585,10 +20582,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20705,10 +20702,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20750,7 +20747,7 @@
       </c>
       <c r="Q149" s="2"/>
       <c r="R149" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="S149" t="s" s="2">
         <v>81</v>
@@ -20827,10 +20824,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20947,10 +20944,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20992,7 +20989,7 @@
       </c>
       <c r="Q151" s="2"/>
       <c r="R151" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="S151" t="s" s="2">
         <v>81</v>
@@ -21069,10 +21066,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21156,7 +21153,7 @@
         <v>81</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
@@ -21177,10 +21174,10 @@
         <v>81</v>
       </c>
       <c r="AM152" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AN152" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AN152" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>81</v>
@@ -21191,10 +21188,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21217,19 +21214,19 @@
         <v>93</v>
       </c>
       <c r="K153" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L153" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L153" t="s" s="2">
+      <c r="M153" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M153" t="s" s="2">
+      <c r="N153" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="N153" t="s" s="2">
+      <c r="O153" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>81</v>
@@ -21278,7 +21275,7 @@
         <v>81</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -21299,10 +21296,10 @@
         <v>81</v>
       </c>
       <c r="AM153" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AN153" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AN153" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>81</v>
@@ -21313,10 +21310,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21342,16 +21339,16 @@
         <v>108</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M154" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M154" t="s" s="2">
+      <c r="N154" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="N154" t="s" s="2">
+      <c r="O154" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>81</v>
@@ -21400,7 +21397,7 @@
         <v>81</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -21421,10 +21418,10 @@
         <v>81</v>
       </c>
       <c r="AM154" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AN154" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AN154" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>81</v>
@@ -21435,10 +21432,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21461,19 +21458,19 @@
         <v>93</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>81</v>
@@ -21501,11 +21498,11 @@
         <v>251</v>
       </c>
       <c r="Y155" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="Z155" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="Z155" t="s" s="2">
-        <v>668</v>
-      </c>
       <c r="AA155" t="s" s="2">
         <v>81</v>
       </c>
@@ -21522,7 +21519,7 @@
         <v>81</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -21540,30 +21537,30 @@
         <v>81</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AM155" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AN155" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AN155" t="s" s="2">
+      <c r="AO155" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP155" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AO155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP155" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D156" t="s" s="2">
         <v>81</v>
@@ -21585,19 +21582,19 @@
         <v>93</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M156" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N156" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="M156" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>621</v>
-      </c>
       <c r="O156" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>81</v>
@@ -21646,7 +21643,7 @@
         <v>81</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21664,27 +21661,27 @@
         <v>81</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AM156" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AN156" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AN156" t="s" s="2">
+      <c r="AO156" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP156" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AO156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP156" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21799,10 +21796,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21919,10 +21916,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21945,19 +21942,19 @@
         <v>93</v>
       </c>
       <c r="K159" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="L159" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="L159" t="s" s="2">
+      <c r="M159" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="M159" t="s" s="2">
+      <c r="N159" t="s" s="2">
         <v>680</v>
       </c>
-      <c r="N159" t="s" s="2">
+      <c r="O159" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>81</v>
@@ -22006,7 +22003,7 @@
         <v>81</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -22027,10 +22024,10 @@
         <v>81</v>
       </c>
       <c r="AM159" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="AN159" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="AN159" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>81</v>
@@ -22041,10 +22038,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22070,22 +22067,22 @@
         <v>172</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M160" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>689</v>
       </c>
       <c r="N160" t="s" s="2">
         <v>312</v>
       </c>
       <c r="O160" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="P160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q160" t="s" s="2">
         <v>690</v>
-      </c>
-      <c r="P160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q160" t="s" s="2">
-        <v>691</v>
       </c>
       <c r="R160" t="s" s="2">
         <v>81</v>
@@ -22109,28 +22106,28 @@
         <v>251</v>
       </c>
       <c r="Y160" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="Z160" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="Z160" t="s" s="2">
+      <c r="AA160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF160" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="AA160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF160" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -22151,10 +22148,10 @@
         <v>81</v>
       </c>
       <c r="AM160" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AN160" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="AN160" t="s" s="2">
-        <v>696</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>81</v>
@@ -22165,10 +22162,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22194,65 +22191,65 @@
         <v>108</v>
       </c>
       <c r="L161" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="M161" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>700</v>
       </c>
       <c r="N161" t="s" s="2">
         <v>312</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q161" s="2"/>
       <c r="R161" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="S161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF161" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="S161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF161" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -22273,10 +22270,10 @@
         <v>81</v>
       </c>
       <c r="AM161" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="AN161" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="AN161" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>81</v>
@@ -22287,10 +22284,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22316,74 +22313,74 @@
         <v>136</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>708</v>
       </c>
-      <c r="M162" t="s" s="2">
+      <c r="N162" t="s" s="2">
         <v>709</v>
       </c>
-      <c r="N162" t="s" s="2">
+      <c r="O162" t="s" s="2">
         <v>710</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>711</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q162" s="2"/>
       <c r="R162" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="S162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF162" t="s" s="2">
         <v>712</v>
       </c>
-      <c r="S162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF162" t="s" s="2">
+      <c r="AG162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH162" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI162" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="AG162" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH162" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI162" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>105</v>
@@ -22395,10 +22392,10 @@
         <v>81</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>81</v>
@@ -22409,10 +22406,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22438,23 +22435,23 @@
         <v>172</v>
       </c>
       <c r="L163" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="M163" t="s" s="2">
         <v>718</v>
       </c>
-      <c r="M163" t="s" s="2">
+      <c r="N163" t="s" s="2">
         <v>719</v>
       </c>
-      <c r="N163" t="s" s="2">
+      <c r="O163" t="s" s="2">
         <v>720</v>
-      </c>
-      <c r="O163" t="s" s="2">
-        <v>721</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q163" s="2"/>
       <c r="R163" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="S163" t="s" s="2">
         <v>81</v>
@@ -22496,7 +22493,7 @@
         <v>81</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
@@ -22517,10 +22514,10 @@
         <v>81</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>81</v>
@@ -22531,10 +22528,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22560,16 +22557,16 @@
         <v>260</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M164" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="M164" t="s" s="2">
+      <c r="N164" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="N164" t="s" s="2">
-        <v>626</v>
-      </c>
       <c r="O164" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>81</v>
@@ -22597,37 +22594,37 @@
         <v>152</v>
       </c>
       <c r="Y164" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="Z164" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="Z164" t="s" s="2">
+      <c r="AA164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF164" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AG164" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH164" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI164" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AA164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF164" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="AG164" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH164" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI164" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>105</v>
@@ -22642,7 +22639,7 @@
         <v>106</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>81</v>
@@ -22653,14 +22650,14 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
@@ -22682,16 +22679,16 @@
         <v>260</v>
       </c>
       <c r="L165" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M165" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M165" t="s" s="2">
+      <c r="N165" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="N165" t="s" s="2">
+      <c r="O165" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>81</v>
@@ -22719,10 +22716,10 @@
         <v>152</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>81</v>
@@ -22740,7 +22737,7 @@
         <v>81</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -22758,27 +22755,27 @@
         <v>81</v>
       </c>
       <c r="AL165" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AM165" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AM165" t="s" s="2">
+      <c r="AN165" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AN165" t="s" s="2">
+      <c r="AO165" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP165" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AO165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP165" t="s" s="2">
-        <v>465</v>
       </c>
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22804,16 +22801,16 @@
         <v>82</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="M166" t="s" s="2">
-        <v>631</v>
-      </c>
       <c r="N166" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O166" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>81</v>
@@ -22862,7 +22859,7 @@
         <v>81</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -22883,10 +22880,10 @@
         <v>81</v>
       </c>
       <c r="AM166" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AN166" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AN166" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>81</v>
@@ -22897,13 +22894,13 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C167" t="s" s="2">
         <v>762</v>
-      </c>
-      <c r="B167" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="C167" t="s" s="2">
-        <v>763</v>
       </c>
       <c r="D167" t="s" s="2">
         <v>81</v>
@@ -22925,19 +22922,19 @@
         <v>93</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="N167" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="O167" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>81</v>
@@ -22986,7 +22983,7 @@
         <v>81</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -23007,10 +23004,10 @@
         <v>81</v>
       </c>
       <c r="AM167" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AN167" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="AN167" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>81</v>
@@ -23021,10 +23018,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23139,10 +23136,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23259,14 +23256,14 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
@@ -23288,10 +23285,10 @@
         <v>115</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M170" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="N170" t="s" s="2">
         <v>118</v>
@@ -23346,7 +23343,7 @@
         <v>81</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
@@ -23381,10 +23378,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23410,16 +23407,16 @@
         <v>260</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="M171" t="s" s="2">
+      <c r="N171" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="N171" t="s" s="2">
-        <v>616</v>
-      </c>
       <c r="O171" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>81</v>
@@ -23447,10 +23444,10 @@
         <v>162</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>81</v>
@@ -23468,7 +23465,7 @@
         <v>81</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>92</v>
@@ -23486,16 +23483,16 @@
         <v>81</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AM171" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AN171" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AN171" t="s" s="2">
+      <c r="AO171" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AO171" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AP171" t="s" s="2">
         <v>81</v>
@@ -23503,10 +23500,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23621,10 +23618,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23741,10 +23738,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23816,7 +23813,7 @@
         <v>81</v>
       </c>
       <c r="AB174" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AC174" s="2"/>
       <c r="AD174" t="s" s="2">
@@ -23861,13 +23858,13 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="C175" t="s" s="2">
         <v>772</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="C175" t="s" s="2">
-        <v>773</v>
       </c>
       <c r="D175" t="s" s="2">
         <v>81</v>
@@ -23985,10 +23982,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24103,10 +24100,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24223,10 +24220,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24268,7 +24265,7 @@
       </c>
       <c r="Q178" s="2"/>
       <c r="R178" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="S178" t="s" s="2">
         <v>81</v>
@@ -24345,10 +24342,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24465,10 +24462,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24494,10 +24491,10 @@
         <v>172</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="N180" t="s" s="2">
         <v>312</v>
@@ -24510,7 +24507,7 @@
       </c>
       <c r="Q180" s="2"/>
       <c r="R180" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="S180" t="s" s="2">
         <v>81</v>
@@ -24587,10 +24584,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24674,7 +24671,7 @@
         <v>81</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>79</v>
@@ -24695,10 +24692,10 @@
         <v>81</v>
       </c>
       <c r="AM181" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AN181" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AN181" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AO181" t="s" s="2">
         <v>81</v>
@@ -24709,10 +24706,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24735,19 +24732,19 @@
         <v>93</v>
       </c>
       <c r="K182" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L182" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L182" t="s" s="2">
+      <c r="M182" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M182" t="s" s="2">
+      <c r="N182" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="N182" t="s" s="2">
+      <c r="O182" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="O182" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>81</v>
@@ -24796,7 +24793,7 @@
         <v>81</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>79</v>
@@ -24817,10 +24814,10 @@
         <v>81</v>
       </c>
       <c r="AM182" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AN182" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AN182" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>81</v>
@@ -24831,10 +24828,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24860,16 +24857,16 @@
         <v>108</v>
       </c>
       <c r="L183" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M183" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M183" t="s" s="2">
+      <c r="N183" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="N183" t="s" s="2">
+      <c r="O183" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="O183" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>81</v>
@@ -24918,7 +24915,7 @@
         <v>81</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
@@ -24939,10 +24936,10 @@
         <v>81</v>
       </c>
       <c r="AM183" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AN183" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AN183" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>81</v>
@@ -24953,10 +24950,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24979,19 +24976,19 @@
         <v>93</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="L184" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M184" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N184" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="M184" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N184" t="s" s="2">
-        <v>621</v>
-      </c>
       <c r="O184" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>81</v>
@@ -25040,7 +25037,7 @@
         <v>81</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>79</v>
@@ -25058,27 +25055,27 @@
         <v>81</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AM184" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AN184" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AN184" t="s" s="2">
+      <c r="AO184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP184" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AO184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP184" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25104,16 +25101,16 @@
         <v>260</v>
       </c>
       <c r="L185" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M185" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="M185" t="s" s="2">
+      <c r="N185" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="N185" t="s" s="2">
-        <v>626</v>
-      </c>
       <c r="O185" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>81</v>
@@ -25141,37 +25138,37 @@
         <v>152</v>
       </c>
       <c r="Y185" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="Z185" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="Z185" t="s" s="2">
+      <c r="AA185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF185" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AG185" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH185" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI185" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AA185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF185" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="AG185" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH185" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI185" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AJ185" t="s" s="2">
         <v>105</v>
@@ -25186,7 +25183,7 @@
         <v>106</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>81</v>
@@ -25197,14 +25194,14 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
@@ -25226,16 +25223,16 @@
         <v>260</v>
       </c>
       <c r="L186" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M186" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M186" t="s" s="2">
+      <c r="N186" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="N186" t="s" s="2">
+      <c r="O186" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="O186" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>81</v>
@@ -25263,10 +25260,10 @@
         <v>152</v>
       </c>
       <c r="Y186" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>81</v>
@@ -25284,7 +25281,7 @@
         <v>81</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
@@ -25302,27 +25299,27 @@
         <v>81</v>
       </c>
       <c r="AL186" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AM186" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AM186" t="s" s="2">
+      <c r="AN186" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AN186" t="s" s="2">
+      <c r="AO186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP186" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AO186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP186" t="s" s="2">
-        <v>465</v>
       </c>
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25348,16 +25345,16 @@
         <v>82</v>
       </c>
       <c r="L187" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M187" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="M187" t="s" s="2">
-        <v>631</v>
-      </c>
       <c r="N187" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O187" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>81</v>
@@ -25406,7 +25403,7 @@
         <v>81</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -25427,10 +25424,10 @@
         <v>81</v>
       </c>
       <c r="AM187" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AN187" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AN187" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="AO187" t="s" s="2">
         <v>81</v>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:42:11+00:00</t>
+    <t>2023-12-08T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-13T10:33:05+00:00</t>
+    <t>2023-12-29T10:04:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T10:04:05+00:00</t>
+    <t>2024-02-01T10:35:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T10:35:02+00:00</t>
+    <t>2024-02-01T13:55:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:55:30+00:00</t>
+    <t>2024-02-01T13:56:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:56:11+00:00</t>
+    <t>2024-02-01T14:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T14:29:51+00:00</t>
+    <t>2024-02-01T16:04:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T16:04:25+00:00</t>
+    <t>2024-02-05T14:48:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T14:48:49+00:00</t>
+    <t>2024-02-12T14:46:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:46:58+00:00</t>
+    <t>2024-02-12T14:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:53:29+00:00</t>
+    <t>2024-04-08T08:01:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>ANS (https://esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
